--- a/knowledge/business_data/DATA005_结构化业务数据_合同台账.xlsx
+++ b/knowledge/business_data/DATA005_结构化业务数据_合同台账.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="H5" s="28" t="n">
-        <v>45371</v>
+        <v>45390</v>
       </c>
       <c r="I5" s="28" t="n">
-        <v>45371</v>
+        <v>45390</v>
       </c>
       <c r="J5" s="28" t="n">
         <v>45453</v>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="H6" s="28" t="n">
-        <v>45495</v>
+        <v>45497</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>45495</v>
+        <v>45497</v>
       </c>
       <c r="J6" s="28" t="n">
         <v>45537</v>
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="H7" s="28" t="n">
-        <v>45427</v>
+        <v>45454</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>45427</v>
+        <v>45454</v>
       </c>
       <c r="J7" s="28" t="n">
         <v>45537</v>
